--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486712_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486712_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.142200000000001</v>
+        <v>9.005800000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.998799999999999</v>
+        <v>8.688599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1434</v>
+        <v>0.3172</v>
       </c>
       <c r="G2" t="n">
         <v>6.7836</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.8204</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.3933</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6009</v>
+        <v>-0.4271</v>
       </c>
       <c r="V2" t="n">
         <v>1.8842</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>E. VIVANCOS ORTIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.227</v>
+        <v>3.1499</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4967</v>
+        <v>2.5586</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.5913</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3514</v>
+        <v>3.0685</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3034</v>
+        <v>1.2554</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6548</v>
+        <v>1.813</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8557</v>
+        <v>3.1378</v>
       </c>
       <c r="K3" t="n">
-        <v>1.628</v>
+        <v>1.8764</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2276</v>
+        <v>1.2615</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5043</v>
+        <v>-0.0693</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9315</v>
+        <v>-0.6209</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4272</v>
+        <v>0.5516</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1239</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1239</v>
+        <v>0.7723</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2483</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.359</v>
+        <v>-0.2277</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1107</v>
+        <v>-0.4825</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.9847</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. VIVANCOS ORTIZ</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9223</v>
+        <v>3.0821</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4552</v>
+        <v>2.3933</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4671</v>
+        <v>0.6889</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0685</v>
+        <v>1.3514</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2554</v>
+        <v>-0.3034</v>
       </c>
       <c r="I4" t="n">
-        <v>1.813</v>
+        <v>1.6548</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1378</v>
+        <v>2.8557</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8764</v>
+        <v>1.628</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2615</v>
+        <v>1.2276</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0693</v>
+        <v>-1.5043</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6209</v>
+        <v>-1.9315</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5516</v>
+        <v>0.4272</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1931</v>
+        <v>2.1239</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7723</v>
+        <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9378</v>
+        <v>-0.3931</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3311</v>
+        <v>-0.4624</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6067</v>
+        <v>0.0693</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9847</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>P. RODRIGUEZ FAJARDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3995</v>
+        <v>1.9993</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9595</v>
+        <v>0.9436</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4399</v>
+        <v>1.0557</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3717</v>
+        <v>3.984</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.124</v>
+        <v>2.0692</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4958</v>
+        <v>1.9148</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3181</v>
+        <v>3.0884</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1921</v>
+        <v>2.5526</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5102</v>
+        <v>0.5359</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9464</v>
+        <v>0.8956</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9319</v>
+        <v>-0.4833</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9856</v>
+        <v>1.379</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1931</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0892</v>
+        <v>-2.1239</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8962</v>
+        <v>0.7723</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9932</v>
+        <v>-0.062</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2753</v>
+        <v>-0.0209</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7178</v>
+        <v>-0.041</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2277</v>
+        <v>-0.5712</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2277</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ FAJARDO</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8296</v>
+        <v>1.9031</v>
       </c>
       <c r="E6" t="n">
-        <v>1.047</v>
+        <v>2.2517</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7825</v>
+        <v>-0.3485</v>
       </c>
       <c r="G6" t="n">
-        <v>3.984</v>
+        <v>2.368</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0692</v>
+        <v>-1.8347</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9148</v>
+        <v>4.2026</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0884</v>
+        <v>3.7276</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5526</v>
+        <v>-0.5927</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5359</v>
+        <v>4.3202</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8956</v>
+        <v>-1.3596</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4833</v>
+        <v>-1.242</v>
       </c>
       <c r="O6" t="n">
-        <v>1.379</v>
+        <v>-0.1176</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1239</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2317</v>
+        <v>-1.1446</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0825</v>
+        <v>-0.5105</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3142</v>
+        <v>-0.6341</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5712</v>
+        <v>-0.2856</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5712</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.448</v>
+        <v>1.6341</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0448</v>
+        <v>0.4424</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5969</v>
+        <v>1.1916</v>
       </c>
       <c r="G7" t="n">
-        <v>2.368</v>
+        <v>0.3717</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8347</v>
+        <v>-2.124</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2026</v>
+        <v>2.4958</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7276</v>
+        <v>1.3181</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5927</v>
+        <v>-0.1921</v>
       </c>
       <c r="L7" t="n">
-        <v>4.3202</v>
+        <v>1.5102</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3596</v>
+        <v>-0.9464</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.242</v>
+        <v>-1.9319</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1176</v>
+        <v>0.9856</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>-3.0892</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9308</v>
+        <v>2.8962</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5998</v>
+        <v>0.2277</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7174</v>
+        <v>-0.2418</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8824</v>
+        <v>0.4695</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1683</v>
+        <v>1.4457</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7199</v>
+        <v>-0.8572</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8882</v>
+        <v>2.3029</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2138</v>
+        <v>0.8871</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7726</v>
+        <v>-0.3382</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9863</v>
+        <v>1.2252</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5049</v>
+        <v>-0.4226</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4958</v>
+        <v>-0.5446</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0008</v>
+        <v>0.1221</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2912</v>
+        <v>1.3096</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2768</v>
+        <v>0.2065</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9856</v>
+        <v>1.1032</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9308</v>
+        <v>-0.1931</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8962</v>
+        <v>0.3862</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6673</v>
+        <v>0.3656</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5797</v>
+        <v>-0.2416</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0876</v>
+        <v>0.6071</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1354</v>
+        <v>0.9738</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1675</v>
+        <v>-0.6165</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3029</v>
+        <v>1.5903</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8871</v>
+        <v>0.2138</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3382</v>
+        <v>-2.7726</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2252</v>
+        <v>2.9863</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4226</v>
+        <v>1.5049</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5446</v>
+        <v>-0.4958</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221</v>
+        <v>2.0008</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3096</v>
+        <v>-1.2912</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2065</v>
+        <v>-2.2768</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1032</v>
+        <v>0.9856</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1931</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3862</v>
+        <v>2.8962</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0553</v>
+        <v>-0.8618</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5518</v>
+        <v>-0.4763</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6071</v>
+        <v>-0.3856</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GONZALEZ-MONJE PEREZ</t>
+          <t>J. MORENO CASTRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6351</v>
+        <v>0.8006</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8005</v>
+        <v>-1.5531</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4356</v>
+        <v>2.3537</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2957</v>
+        <v>0.1842</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4276</v>
+        <v>-1.3033</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8681</v>
+        <v>1.4875</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7442</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7035</v>
+        <v>0.0074</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0407</v>
+        <v>0.6534</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5514</v>
+        <v>-0.4766</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2759</v>
+        <v>-1.3107</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8274</v>
+        <v>0.8341</v>
       </c>
       <c r="P10" t="n">
         <v>-0.7723</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1585</v>
+        <v>-2.1239</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3974</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3863</v>
+        <v>-0.09</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7836</v>
+        <v>0.1658</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2856</v>
+        <v>1.3129</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2856</v>
+        <v>1.3129</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MORENO CASTRO</t>
+          <t>M. GONZALEZ-MONJE PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5978</v>
+        <v>0.4654</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6565</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2544</v>
+        <v>1.1625</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1842</v>
+        <v>1.2957</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3033</v>
+        <v>0.4276</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4875</v>
+        <v>0.8681</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.7442</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0074</v>
+        <v>0.7035</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6534</v>
+        <v>0.0407</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4766</v>
+        <v>0.5514</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3107</v>
+        <v>-0.2759</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8341</v>
+        <v>0.8274</v>
       </c>
       <c r="P11" t="n">
         <v>-0.7723</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1239</v>
+        <v>-1.1585</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.127</v>
+        <v>0.2276</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1934</v>
+        <v>-0.2829</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0665</v>
+        <v>0.5105</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3129</v>
+        <v>-0.2856</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.3129</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5275</v>
+        <v>-2.5772</v>
       </c>
       <c r="E12" t="n">
         <v>-2.9984</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4708</v>
+        <v>0.4212</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3193</v>
@@ -1390,13 +1390,13 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1157</v>
+        <v>-0.1654</v>
       </c>
       <c r="T12" t="n">
         <v>0.1377</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2534</v>
+        <v>-0.303</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.9777</v>
+        <v>21.8826</v>
       </c>
       <c r="E13" t="n">
-        <v>10.6592</v>
+        <v>10.5559</v>
       </c>
       <c r="F13" t="n">
-        <v>11.3182</v>
+        <v>11.3268</v>
       </c>
       <c r="G13" t="n">
         <v>18.1887</v>
@@ -1468,16 +1468,16 @@
         <v>16.798</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.1657</v>
+        <v>-3.260800000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.7063</v>
+        <v>-2.809699999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4595000000000001</v>
+        <v>-0.4511000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>4.638000000000001</v>
+        <v>4.638</v>
       </c>
       <c r="W13" t="n">
         <v>6.709599999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6337</v>
+        <v>4.2239</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1702</v>
+        <v>3.4805</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4635</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>4.6052</v>
@@ -1546,13 +1546,13 @@
         <v>1.5446</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3961</v>
+        <v>0.9862</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3314</v>
+        <v>-0.0212</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7276</v>
+        <v>1.0074</v>
       </c>
       <c r="V14" t="n">
         <v>1.1424</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5723</v>
+        <v>1.8536</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5235</v>
+        <v>1.7304</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0488</v>
+        <v>0.1233</v>
       </c>
       <c r="G15" t="n">
         <v>0.7309</v>
@@ -1624,13 +1624,13 @@
         <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0771</v>
+        <v>0.3584</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1107</v>
+        <v>0.0961</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1878</v>
+        <v>0.2623</v>
       </c>
       <c r="V15" t="n">
         <v>0.5712</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.419</v>
+        <v>1.1914</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0474</v>
+        <v>-0.056</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3716</v>
+        <v>1.2475</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7466</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7448</v>
+        <v>0.5173</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1377</v>
+        <v>0.0342</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6072</v>
+        <v>0.483</v>
       </c>
       <c r="V16" t="n">
         <v>1.2277</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7338</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2792</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.438</v>
+        <v>0.6615</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4344</v>
@@ -1780,13 +1780,13 @@
         <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0994</v>
+        <v>-0.0827</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3032</v>
+        <v>0.0964</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4026</v>
+        <v>-0.1791</v>
       </c>
       <c r="V17" t="n">
         <v>0.2856</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0328</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9465</v>
+        <v>0.7396</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9137</v>
+        <v>-0.8144</v>
       </c>
       <c r="G18" t="n">
         <v>0.655</v>
@@ -1858,13 +1858,13 @@
         <v>0.5792</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3971</v>
+        <v>0.2896</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3307</v>
+        <v>0.1239</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0663</v>
+        <v>0.1657</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5985</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.522</v>
+        <v>-1.1869</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2072</v>
+        <v>0.1031</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3148</v>
+        <v>-1.2899</v>
       </c>
       <c r="G19" t="n">
         <v>-0.373</v>
@@ -1936,13 +1936,13 @@
         <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.149</v>
+        <v>0.1861</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1655</v>
+        <v>0.1447</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6138</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6329</v>
+        <v>-2.8687</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0201</v>
+        <v>-2.3304</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6128</v>
+        <v>-0.5383</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2135</v>
@@ -2014,13 +2014,13 @@
         <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0333</v>
+        <v>-0.2691</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1928</v>
+        <v>-0.1174</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2261</v>
+        <v>-0.1516</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>I. MARTINEZ PARDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6306</v>
+        <v>-4.6093</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3189</v>
+        <v>-1.0908</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3117</v>
+        <v>-3.5185</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.5129</v>
+        <v>-3.4368</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6206</v>
+        <v>-1.1174</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8922</v>
+        <v>-2.3195</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1875</v>
+        <v>0.7783</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3096</v>
+        <v>0.8144</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1221</v>
+        <v>-0.0361</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3253</v>
+        <v>-4.2151</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.311</v>
+        <v>-1.9318</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0143</v>
+        <v>-2.2833</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3169</v>
+        <v>-2.1239</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8823</v>
+        <v>0.5999</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1855</v>
+        <v>0.2547</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3033</v>
+        <v>0.3451</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2277</v>
+        <v>-0.6138</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2277</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7094</v>
+        <v>-4.6804</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1358</v>
+        <v>-4.0324</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5736</v>
+        <v>-0.6481</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1794</v>
@@ -2170,13 +2170,13 @@
         <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0606</v>
+        <v>0.0895</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3038</v>
+        <v>-0.2004</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3644</v>
+        <v>0.2899</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1698</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PARDO</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7954</v>
+        <v>-4.9996</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4011</v>
+        <v>-4.0125</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3943</v>
+        <v>-0.9871</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4368</v>
+        <v>-4.2383</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1174</v>
+        <v>-0.7863</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3195</v>
+        <v>-3.452</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7783</v>
+        <v>-1.789</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8144</v>
+        <v>0.3178</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0361</v>
+        <v>-2.1068</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.2151</v>
+        <v>-2.4492</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9318</v>
+        <v>-1.1041</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.2833</v>
+        <v>-1.3451</v>
       </c>
       <c r="P23" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-1.1585</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-2.1239</v>
-      </c>
       <c r="R23" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4137</v>
+        <v>-0.2553</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0555</v>
+        <v>-0.3659</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4693</v>
+        <v>0.1106</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6138</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="W23" t="n">
+        <v>-0.6991000000000001</v>
+      </c>
+      <c r="X23" t="n">
         <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-0.6138</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0037</v>
+        <v>-5.0855</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1159</v>
+        <v>-2.1463</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8878</v>
+        <v>-2.9392</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.2383</v>
+        <v>-3.5129</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7863</v>
+        <v>-1.6206</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.452</v>
+        <v>-1.8922</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.789</v>
+        <v>-0.1875</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3178</v>
+        <v>-0.3096</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.1068</v>
+        <v>0.1221</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4492</v>
+        <v>-3.3253</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1041</v>
+        <v>-1.311</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3451</v>
+        <v>-2.0143</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1931</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1585</v>
+        <v>-2.3169</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3515</v>
+        <v>1.5446</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2594</v>
+        <v>0.4274</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4693</v>
+        <v>0.3581</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2099</v>
+        <v>0.0692</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-1.2277</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6991000000000001</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.2723</v>
+        <v>-6.6888</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1699</v>
+        <v>-3.8597</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1023</v>
+        <v>-2.8292</v>
       </c>
       <c r="G25" t="n">
         <v>-5.8226</v>
@@ -2404,13 +2404,13 @@
         <v>1.7377</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1215</v>
+        <v>0.462</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1659</v>
+        <v>0.1444</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0444</v>
+        <v>0.3176</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9421</v>
@@ -2443,13 +2443,13 @@
         <v>-11.4021</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.7891</v>
+        <v>-10.789</v>
       </c>
       <c r="G26" t="n">
         <v>-17.9664</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1031</v>
+        <v>3.103100000000001</v>
       </c>
       <c r="I26" t="n">
         <v>-21.0695</v>
@@ -2482,13 +2482,13 @@
         <v>14.4806</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3091</v>
+        <v>3.3093</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5477999999999998</v>
+        <v>0.5475999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>2.7615</v>
+        <v>2.761499999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-4.6379</v>
